--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23029"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D82277-B24B-4B2B-B76F-5FEB52F51472}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -59,9 +60,6 @@
     <t>Same Day Timing ID</t>
   </si>
   <si>
-    <t>Mode of Payment ID</t>
-  </si>
-  <si>
     <t>Item Product Type ID</t>
   </si>
   <si>
@@ -84,18 +82,12 @@
   </si>
   <si>
     <t>Consignee City Name</t>
-  </si>
-  <si>
-    <t>Charges Mode ID</t>
-  </si>
-  <si>
-    <t>Delivery Type ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -441,99 +433,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="O1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D82277-B24B-4B2B-B76F-5FEB52F51472}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514E1BD1-2D8F-4CC6-8EAF-905D2E9588AE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Product Value</t>
-  </si>
-  <si>
-    <t>Collection Amount</t>
   </si>
   <si>
     <t>Consignee Phone Number 2 (03000000000)</t>
@@ -434,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -454,12 +451,13 @@
     <col min="16" max="16" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -467,7 +465,7 @@
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -476,10 +474,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -514,9 +512,7 @@
       <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="V1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514E1BD1-2D8F-4CC6-8EAF-905D2E9588AE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7BEB0C-AF5A-4A97-86E1-85449C125775}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -451,13 +451,9 @@
     <col min="16" max="16" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -512,7 +508,6 @@
       <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="V1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7BEB0C-AF5A-4A97-86E1-85449C125775}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F1AFAF-5E40-4CCB-BC66-5E0C6204E2CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Consignee City Name</t>
+  </si>
+  <si>
+    <t>Order Date  (YYYY-MM-DD)</t>
   </si>
 </sst>
 </file>
@@ -431,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -442,18 +445,19 @@
     <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.21875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -482,30 +486,33 @@
         <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F1AFAF-5E40-4CCB-BC66-5E0C6204E2CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6A83F7-125A-4B05-AE60-CBDC87CA5BBC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -82,6 +82,21 @@
   </si>
   <si>
     <t>Order Date  (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 1</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 2</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 3</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 4</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 5</t>
   </si>
 </sst>
 </file>
@@ -434,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -455,9 +470,10 @@
     <col min="17" max="17" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -514,6 +530,21 @@
       </c>
       <c r="S1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6A83F7-125A-4B05-AE60-CBDC87CA5BBC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DE3603-F714-4169-8BBC-6BC2D0559E35}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Shipper Reference Number 5</t>
+  </si>
+  <si>
+    <t>Delivery Type ID</t>
   </si>
 </sst>
 </file>
@@ -449,101 +452,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DE3603-F714-4169-8BBC-6BC2D0559E35}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271EC45A-588F-41BB-874C-2073ABF0630D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Shipper Reference Number 5</t>
-  </si>
-  <si>
-    <t>Delivery Type ID</t>
   </si>
 </sst>
 </file>
@@ -452,105 +449,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
       <c r="U1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271EC45A-588F-41BB-874C-2073ABF0630D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345C9C3F-49EC-4091-A588-8D83B697EFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Shipper Reference Number 5</t>
+  </si>
+  <si>
+    <t>Open Shipment</t>
   </si>
 </sst>
 </file>
@@ -449,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -473,7 +476,7 @@
     <col min="20" max="24" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -545,6 +548,9 @@
       </c>
       <c r="X1" t="s">
         <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345C9C3F-49EC-4091-A588-8D83B697EFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -100,12 +99,18 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Consignee Address Latitude</t>
+  </si>
+  <si>
+    <t>Consignee Address Longitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -451,8 +456,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -462,21 +467,22 @@
     <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="21.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -502,54 +508,60 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>24</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Reverse Pickup Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>Consignee Address Longitude</t>
+  </si>
+  <si>
+    <t>Retail Pickup Store ID</t>
+  </si>
+  <si>
+    <t>Retail Deliver Store ID</t>
   </si>
 </sst>
 </file>
@@ -457,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -482,7 +488,7 @@
     <col min="22" max="26" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -563,6 +569,12 @@
       </c>
       <c r="AA1" t="s">
         <v>24</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
